--- a/artfynd/A 15886-2026 artfynd.xlsx
+++ b/artfynd/A 15886-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91983196</v>
+        <v>117060204</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>102623</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malmen, vid avtag skogsbilväg mot Brölundaåsen, Upl</t>
+          <t>Brovägen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709012.0892759573</v>
+        <v>709039</v>
       </c>
       <c r="R2" t="n">
-        <v>6642196.681976236</v>
+        <v>6642154</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sporadisk sång, strax syd om allmänna vägen vid Malmen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +787,252 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91983196</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Malmen, vid avtag skogsbilväg mot Brölundaåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>709012</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6642197</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>78499528</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brovägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>709039</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6642154</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
